--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/TEXAS_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/TEXAS_2016.xlsx
@@ -949,7 +949,7 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="34">
@@ -1291,7 +1291,7 @@
         <v>17</v>
       </c>
       <c r="D52">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="53">
@@ -1993,7 +1993,7 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="92">
@@ -2029,7 +2029,7 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="94">
@@ -2677,7 +2677,7 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="130">
@@ -2767,7 +2767,7 @@
         <v>17</v>
       </c>
       <c r="D134">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="135">
@@ -2857,7 +2857,7 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="140">
@@ -3163,7 +3163,7 @@
         <v>17</v>
       </c>
       <c r="D156">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="157">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C195">
@@ -4063,7 +4063,7 @@
         <v>1592</v>
       </c>
       <c r="D206">
-        <v>0.009082299784352431</v>
+        <v>0.009082299784352432</v>
       </c>
     </row>
     <row r="207">
@@ -4297,7 +4297,7 @@
         <v>169</v>
       </c>
       <c r="D219">
-        <v>0.0009641386077610305</v>
+        <v>0.0009641386077610304</v>
       </c>
     </row>
     <row r="220">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C260">
@@ -5179,7 +5179,7 @@
         <v>171</v>
       </c>
       <c r="D268">
-        <v>0.0009755485321132321</v>
+        <v>0.000975548532113232</v>
       </c>
     </row>
     <row r="269">
@@ -6313,7 +6313,7 @@
         <v>17</v>
       </c>
       <c r="D331">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="332">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C421">
@@ -8239,7 +8239,7 @@
         <v>1591</v>
       </c>
       <c r="D438">
-        <v>0.009076594822176329</v>
+        <v>0.009076594822176327</v>
       </c>
     </row>
     <row r="439">
@@ -10741,7 +10741,7 @@
         <v>165</v>
       </c>
       <c r="D577">
-        <v>0.0009413187590566275</v>
+        <v>0.0009413187590566276</v>
       </c>
     </row>
     <row r="578">
@@ -10813,7 +10813,7 @@
         <v>17</v>
       </c>
       <c r="D581">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="582">
@@ -10831,7 +10831,7 @@
         <v>17</v>
       </c>
       <c r="D582">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="583">
@@ -13009,7 +13009,7 @@
         <v>17</v>
       </c>
       <c r="D703">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="704">
@@ -13099,7 +13099,7 @@
         <v>17</v>
       </c>
       <c r="D708">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="709">
@@ -14035,7 +14035,7 @@
         <v>17</v>
       </c>
       <c r="D760">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="761">
@@ -14341,7 +14341,7 @@
         <v>17</v>
       </c>
       <c r="D777">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="778">
@@ -16800,7 +16800,7 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C914">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C916">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="B917" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C917">
@@ -17221,7 +17221,7 @@
         <v>17</v>
       </c>
       <c r="D937">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="938">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1055">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="B1093" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1093">
@@ -21217,7 +21217,7 @@
         <v>17</v>
       </c>
       <c r="D1159">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="1160">
@@ -21469,7 +21469,7 @@
         <v>17</v>
       </c>
       <c r="D1173">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="1174">
@@ -23305,7 +23305,7 @@
         <v>17</v>
       </c>
       <c r="D1275">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="1276">
@@ -23989,7 +23989,7 @@
         <v>17</v>
       </c>
       <c r="D1313">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="1314">
@@ -25825,7 +25825,7 @@
         <v>17</v>
       </c>
       <c r="D1415">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="1416">
@@ -26221,7 +26221,7 @@
         <v>17</v>
       </c>
       <c r="D1437">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="1438">
@@ -26653,7 +26653,7 @@
         <v>158</v>
       </c>
       <c r="D1461">
-        <v>0.0009013840238239221</v>
+        <v>0.000901384023823922</v>
       </c>
     </row>
     <row r="1462">
@@ -28759,7 +28759,7 @@
         <v>165</v>
       </c>
       <c r="D1578">
-        <v>0.0009413187590566275</v>
+        <v>0.0009413187590566276</v>
       </c>
     </row>
     <row r="1579">
@@ -30379,7 +30379,7 @@
         <v>17</v>
       </c>
       <c r="D1668">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="1669">
@@ -31567,7 +31567,7 @@
         <v>163</v>
       </c>
       <c r="D1734">
-        <v>0.0009299088347044259</v>
+        <v>0.000929908834704426</v>
       </c>
     </row>
     <row r="1735">
@@ -32611,7 +32611,7 @@
         <v>171</v>
       </c>
       <c r="D1792">
-        <v>0.0009755485321132321</v>
+        <v>0.000975548532113232</v>
       </c>
     </row>
     <row r="1793">
@@ -33997,7 +33997,7 @@
         <v>17</v>
       </c>
       <c r="D1869">
-        <v>9.698435699371313E-05</v>
+        <v>9.698435699371312E-05</v>
       </c>
     </row>
     <row r="1870">
